--- a/Assets/Colors.xlsx
+++ b/Assets/Colors.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexs\Vectoid\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857C596F-A825-4AB0-AD3B-044096F77275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45B0B49-4792-488F-9B2F-8D9A82B663F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9643E470-58B8-4DC6-BA34-2D595144B412}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="87">
   <si>
     <t>Cyan</t>
   </si>
@@ -59,33 +60,12 @@
     <t>Green</t>
   </si>
   <si>
-    <t>Teal</t>
-  </si>
-  <si>
-    <t>#008080</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>#800080</t>
-  </si>
-  <si>
-    <t>Olive</t>
-  </si>
-  <si>
-    <t>#808000</t>
-  </si>
-  <si>
     <t>Black</t>
   </si>
   <si>
     <t>#000000</t>
   </si>
   <si>
-    <t>Brown</t>
-  </si>
-  <si>
     <t>Tier 2</t>
   </si>
   <si>
@@ -107,9 +87,6 @@
     <t>#00FF00</t>
   </si>
   <si>
-    <t>#663300</t>
-  </si>
-  <si>
     <t>Cerulean</t>
   </si>
   <si>
@@ -146,33 +123,6 @@
     <t>#AAFF00</t>
   </si>
   <si>
-    <t>Blue + Green</t>
-  </si>
-  <si>
-    <t>Red + Blue</t>
-  </si>
-  <si>
-    <t>Red + Green</t>
-  </si>
-  <si>
-    <t>Blue + Cyan</t>
-  </si>
-  <si>
-    <t>Green + Cyan</t>
-  </si>
-  <si>
-    <t>Blue + Magenta</t>
-  </si>
-  <si>
-    <t>Red + Magenta</t>
-  </si>
-  <si>
-    <t>Green + Yellow</t>
-  </si>
-  <si>
-    <t>Red + Yellow</t>
-  </si>
-  <si>
     <t>Tier 4</t>
   </si>
   <si>
@@ -185,66 +135,15 @@
     <t>Cyan + Yellow</t>
   </si>
   <si>
-    <t>Cyan + Magenta + Yellow</t>
-  </si>
-  <si>
     <t>Dreieck</t>
   </si>
   <si>
-    <t>5eck</t>
-  </si>
-  <si>
-    <t>1Cyan+1Magenta+1Yellow</t>
-  </si>
-  <si>
-    <t>2Cyan+1Magenta+1Yellow</t>
-  </si>
-  <si>
-    <t>1Cyan+2Magenta+1Yellow</t>
-  </si>
-  <si>
-    <t>1Cyan+1Magenta+2Yellow</t>
-  </si>
-  <si>
-    <t>3Cyan+0Magenta+1Yellow</t>
-  </si>
-  <si>
-    <t>0Cyan+3Magenta+1Yellow</t>
-  </si>
-  <si>
-    <t>0Cyan+1Magenta+3Yellow</t>
-  </si>
-  <si>
-    <t>1Cyan+0Magenta+3Yellow</t>
-  </si>
-  <si>
-    <t>2Cyan+2Magenta+0Yellow</t>
-  </si>
-  <si>
-    <t>0Cyan+2Magenta+2Yellow</t>
-  </si>
-  <si>
-    <t>2Cyan+0Magenta+2Yellow</t>
-  </si>
-  <si>
-    <t>3Cyan+1Magenta+0Yellow</t>
-  </si>
-  <si>
-    <t>1Cyan+3Magenta+0Yellow</t>
-  </si>
-  <si>
     <t>Prism Mischverhältnisse</t>
   </si>
   <si>
     <t>Tier 5</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Any 4 Tier 4 colors</t>
-  </si>
-  <si>
     <t>#FFFF00</t>
   </si>
   <si>
@@ -272,27 +171,9 @@
     <t>Jeder Treffer verlangsamt das getroffene Ziel geringfügig. Der Slow ist bewusst deutlich schwächer als der Effekt von Blue.</t>
   </si>
   <si>
-    <t>Stacking Slow</t>
-  </si>
-  <si>
-    <t>Decaying Burn</t>
-  </si>
-  <si>
     <t>Poison</t>
   </si>
   <si>
-    <t>Tier-2 Amplifier</t>
-  </si>
-  <si>
-    <t>Cyan-Spectrum Amplifier</t>
-  </si>
-  <si>
-    <t>Magenta-Spectrum Amplifier</t>
-  </si>
-  <si>
-    <t>Yellow-Spectrum Amplifier</t>
-  </si>
-  <si>
     <t>Freeze</t>
   </si>
   <si>
@@ -305,9 +186,6 @@
     <t>Vulnerability</t>
   </si>
   <si>
-    <t>Permanent Burn</t>
-  </si>
-  <si>
     <t>Scaling Chain Lightning</t>
   </si>
   <si>
@@ -329,55 +207,110 @@
     <t>Ein Treffer setzt den Green-Poison-Effekt auf 10 Stacks. Der Poison verursacht bei 10 Stacks seinen maximalen Schaden und verliert anschließend automatisch 1 Stack pro Sekunde. Jeder weitere Green-Treffer setzt den Stack-Wert wieder auf 10, statt zusätzliche Stacks hinzuzufügen.</t>
   </si>
   <si>
-    <t>Trifft Brown ein Ziel, das bereits mindestens einen Blue-, Red- oder Green-Stack besitzt, wird der jeweilige vorhandene Effekt um +1 Stack erhöht. Brown kann dadurch bestehende Tier-2-Effekte verlängern oder verstärken, erzeugt diese Effekte aber nicht selbst.</t>
-  </si>
-  <si>
-    <t>Erhöht die Menge an Cerulean- und Aquamarine-Stacks, die das Ziel durch zukünftige Treffer erhält, um einen festgelegten Prozentsatz. Teal verstärkt damit die cyan-dominanten Tier-4-Effekte.</t>
-  </si>
-  <si>
-    <t>Erhöht die Menge an Violet- und Fuchsia-Stacks, die das Ziel durch zukünftige Treffer erhält, um einen festgelegten Prozentsatz. Purple verstärkt damit die magenta-dominanten Tier-4-Effekte.</t>
-  </si>
-  <si>
-    <t>Erhöht die Menge an Amber- und Chartreuse-Stacks, die das Ziel durch zukünftige Treffer erhält, um einen festgelegten Prozentsatz. Olive verstärkt damit die yellow-dominanten Tier-4-Effekte.</t>
-  </si>
-  <si>
     <t>Treffer bauen Cerulean Stacks von 0–30 auf. Sobald der definierte Freeze-Schwellenwert erreicht wird, wird das Ziel für 1 Sekunde vollständig eingefroren. Nach Auslösung des Freeze-Effekts werden die dafür benötigten Stacks verbraucht bzw. zurückgesetzt.</t>
   </si>
   <si>
-    <t>Aquamarine überträgt vorhandene Tier-4-Stacks des getroffenen Gegners auf Gegner in seiner Nähe. Übertragen werden maximal 50 % der aktuellen Stacks. Durch Aquamarine kopierte Stacks können nicht erneut durch Aquamarine weiterverbreitet werden, wodurch Kettenreaktionen verhindert werden.</t>
-  </si>
-  <si>
     <t>Treffer bauen Violet Stacks von 0–30 auf. Beim Erreichen des definierten Schwellenwerts explodiert das Ziel und verursacht Flächenschaden in seiner Umgebung. Die Explosion verursacht 3 % der maximalen Lebenspunkte des auslösenden Gegners als Schaden. Nach der Explosion werden die dafür benötigten Violet Stacks verbraucht bzw. zurückgesetzt.</t>
   </si>
   <si>
     <t>Treffer bauen Fuchsia Stacks von 0–100 auf. Mit jedem Stack erhöht sich der Schaden, den das Ziel aus allen Schadensquellen erhält. Bei 100 Stacks ist der Effekt auf maximal +10 % Damage Taken begrenzt.</t>
   </si>
   <si>
-    <t>Treffer bauen Amber Stacks von 0–100 auf. Die Stacks erzeugen einen permanenten Burn-Effekt, der nicht von selbst abklingt. Der Schaden steigt mit der Anzahl der Stacks und erreicht bei 100 Stacks maximal 1 % der maximalen Lebenspunkte des Gegners pro Sekunde.</t>
-  </si>
-  <si>
-    <t>Treffer bauen Chartreuse Stacks von 0–100 auf. Mit steigender Stack-Anzahl erhöht sich die Anzahl der Ziele, auf die der Lightning-Effekt überspringen kann. Der Effekt kann maximal 10 Gegner pro Auslösung treffen.</t>
-  </si>
-  <si>
     <t>Jeder Black-Treffer erhöht die Execute-Schwelle um 0,1 Prozentpunkte. Liegen die aktuellen Lebenspunkte des Gegners unterhalb dieser Schwelle, kann ein Black-Treffer ihn sofort töten. Black Stacks bleiben 5 Sekunden erhalten und werden durch weitere Black-Treffer erneuert. Die Execute-Prüfung wird ausschließlich durch einen Black-Treffer ausgelöst; Schaden anderer Farben kann den Gegner zwar unter die Schwelle bringen, führt aber nicht automatisch zum Execute.</t>
+  </si>
+  <si>
+    <t>2Magenta + Cyan + Yellow</t>
+  </si>
+  <si>
+    <t>Magenta + 2 Cyan + Yellow</t>
+  </si>
+  <si>
+    <t>Sechseck</t>
+  </si>
+  <si>
+    <t>Magenta + Cyan +2 Yellow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 5 </t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Cerulean + Violet + Amber</t>
+  </si>
+  <si>
+    <t>Aquamarine + Fuchsia + Chartreuse</t>
+  </si>
+  <si>
+    <t>#FFFFFF</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
+    <t>Slow</t>
+  </si>
+  <si>
+    <t>Aquamarine überträgt vorhandene Tier-3-Stacks des getroffenen Gegners auf Gegner in seiner Nähe. Übertragen werden maximal 50 % der aktuellen Stacks. Durch Aquamarine kopierte Stacks können nicht erneut durch Aquamarine weiterverbreitet werden, wodurch Kettenreaktionen verhindert werden.</t>
+  </si>
+  <si>
+    <t>Cerulean + cyan</t>
+  </si>
+  <si>
+    <t>Blue + green</t>
+  </si>
+  <si>
+    <t>Red + blue</t>
+  </si>
+  <si>
+    <t>Green + red</t>
+  </si>
+  <si>
+    <t>Magenta + 3 Cyan + Yellow</t>
+  </si>
+  <si>
+    <t>Violet + magenta</t>
+  </si>
+  <si>
+    <t>3Magenta + Cyan + Yellow</t>
+  </si>
+  <si>
+    <t>Magenta + Cyan +3 Yellow</t>
+  </si>
+  <si>
+    <t>Chartreuse + yellow</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>Mix with triangle prism</t>
+  </si>
+  <si>
+    <t>Mix with hexagonal prism</t>
+  </si>
+  <si>
+    <t>Consumes all stacks of all colors to deal high amount of dmg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulling enemies together in a range. </t>
+  </si>
+  <si>
+    <t>Treffer bauen Chartreuse Stacks von 0–100 auf. Mit steigender Stack-Anzahl erhöht sich die Anzahl der Ziele, auf die der Lightning-Effekt überspringen kann. Der Effekt hat eine range vom ursprungsenemy aus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -396,7 +329,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,30 +374,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF008080"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF800080"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF808000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF663300"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00AAFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -501,7 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -526,33 +441,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -901,493 +814,429 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394BB268-02A1-434A-9951-D9B1B6DAC922}">
-  <dimension ref="E2:S23"/>
+  <dimension ref="D2:M31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="2.85546875" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
+    <col min="8" max="8" width="38.140625" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="255.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="41.28515625" customWidth="1"/>
     <col min="16" max="16" width="28.140625" customWidth="1"/>
     <col min="17" max="17" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E2" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-    </row>
-    <row r="3" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E3" s="3" t="s">
-        <v>2</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E3" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+        <v>36</v>
+      </c>
       <c r="I3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-    </row>
-    <row r="4" spans="5:19" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-    </row>
-    <row r="5" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E5" s="1" t="s">
-        <v>0</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="19"/>
+        <v>34</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="14"/>
       <c r="I5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="J5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" t="s">
         <v>75</v>
       </c>
-      <c r="K5" t="s">
+      <c r="I15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
         <v>76</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-    </row>
-    <row r="6" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" t="s">
         <v>49</v>
       </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-    </row>
-    <row r="7" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K7" t="s">
-        <v>93</v>
-      </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-    </row>
-    <row r="8" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" t="s">
-        <v>94</v>
-      </c>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-    </row>
-    <row r="9" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" t="s">
-        <v>95</v>
-      </c>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-    </row>
-    <row r="10" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10" t="s">
-        <v>96</v>
-      </c>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-    </row>
-    <row r="11" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="I11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-    </row>
-    <row r="12" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E12" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12" t="s">
-        <v>97</v>
-      </c>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-    </row>
-    <row r="13" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" t="s">
-        <v>82</v>
-      </c>
-      <c r="K13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E15" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" t="s">
         <v>84</v>
       </c>
-      <c r="K16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" t="s">
-        <v>55</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E18" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" t="s">
-        <v>63</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J18" t="s">
-        <v>86</v>
-      </c>
-      <c r="K18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E20" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" t="s">
-        <v>88</v>
-      </c>
-      <c r="K20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E21" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>58</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E22" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" t="s">
-        <v>67</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="J23" t="s">
-        <v>90</v>
-      </c>
-      <c r="K23" t="s">
-        <v>106</v>
-      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+    </row>
+    <row r="29" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1396,4 +1245,433 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501A01B5-51F1-47A1-A511-3A35A4A16469}">
+  <dimension ref="B8:S30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="I12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="O12" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="21"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="22"/>
+      <c r="I15" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="I16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="I19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C20" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="I22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="I23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="17"/>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="C28" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>